--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_373_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_373_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6961</v>
+        <v>4.5452</v>
       </c>
       <c r="E2" t="n">
-        <v>1.904</v>
+        <v>2.0219</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7921</v>
+        <v>2.5232</v>
       </c>
       <c r="G2" t="n">
         <v>3.4613</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1625</v>
+        <v>0.0116</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4832</v>
+        <v>-0.3653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6458</v>
+        <v>0.3769</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6327</v>
+        <v>3.7502</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5985</v>
+        <v>2.4103</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9658</v>
+        <v>1.3398</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4875</v>
+        <v>1.3746</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3168</v>
+        <v>-0.7166</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1707</v>
+        <v>2.0912</v>
       </c>
       <c r="J3" t="n">
-        <v>0.777</v>
+        <v>1.7575</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.1883</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6993</v>
+        <v>1.5692</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2895</v>
+        <v>-0.3829</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2391</v>
+        <v>-0.9049</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5286</v>
+        <v>0.5221</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5396</v>
+        <v>1.2158</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4812</v>
+        <v>0.6528</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0584</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5002</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1884</v>
+        <v>3.2167</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8821</v>
+        <v>3.9472</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3062</v>
+        <v>-0.7306</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3746</v>
+        <v>0.4875</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7166</v>
+        <v>0.3168</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0912</v>
+        <v>0.1707</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7575</v>
+        <v>0.777</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1883</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5692</v>
+        <v>0.6993</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3829</v>
+        <v>-0.2895</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9049</v>
+        <v>0.2391</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5221</v>
+        <v>-0.5286</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.654</v>
+        <v>1.1235</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1246</v>
+        <v>0.8298</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5294</v>
+        <v>0.2937</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2417</v>
+        <v>2.4276</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0455</v>
+        <v>1.3994</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1962</v>
+        <v>1.0282</v>
       </c>
       <c r="G5" t="n">
         <v>1.3902</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3598</v>
+        <v>-0.174</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3791</v>
+        <v>0.2111</v>
       </c>
       <c r="V5" t="n">
         <v>0.2836</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8607</v>
+        <v>1.9949</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5184</v>
+        <v>2.2526</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3423</v>
+        <v>-0.2577</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6107</v>
+        <v>2.6194</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5739</v>
+        <v>1.2509</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0368</v>
+        <v>1.3686</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5585</v>
+        <v>2.0583</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6456</v>
+        <v>0.8437</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0871</v>
+        <v>1.2146</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1692</v>
+        <v>0.5611</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2195</v>
+        <v>0.4071</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0502</v>
+        <v>0.154</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>2.327</v>
+        <v>-0.1759</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2072</v>
+        <v>-0.3418</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1198</v>
+        <v>0.1658</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.624</v>
+        <v>1.7057</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7808</v>
+        <v>-0.8583</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1569</v>
+        <v>2.5639</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6194</v>
+        <v>-0.3298</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2509</v>
+        <v>-0.5473</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3686</v>
+        <v>0.2174</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0583</v>
+        <v>-0.9764</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8437</v>
+        <v>-0.6183</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2146</v>
+        <v>-0.3581</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5611</v>
+        <v>0.6466</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4071</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.154</v>
+        <v>0.5756</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.4118</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8136</v>
+        <v>0.1182</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2667</v>
+        <v>0.2937</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7627</v>
+        <v>1.186</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.566</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3287</v>
+        <v>2.0565</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3298</v>
+        <v>1.3158</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5473</v>
+        <v>0.4391</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2174</v>
+        <v>0.8767</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9764</v>
+        <v>1.209</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6183</v>
+        <v>0.9046</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3581</v>
+        <v>0.3044</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6466</v>
+        <v>0.1068</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.4655</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5756</v>
+        <v>0.5723</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5311</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5895</v>
+        <v>0.2401</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0584</v>
+        <v>0.326</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NAKIC</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2577</v>
+        <v>1.0699</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3063</v>
+        <v>0.1645</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0485</v>
+        <v>0.9054</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4229</v>
+        <v>-0.6107</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4261</v>
+        <v>-0.5739</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0033</v>
+        <v>-0.0368</v>
       </c>
       <c r="J9" t="n">
-        <v>0.605</v>
+        <v>0.5585</v>
       </c>
       <c r="K9" t="n">
-        <v>0.605</v>
+        <v>0.6456</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.0871</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1821</v>
+        <v>-1.1692</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1788</v>
+        <v>-1.2195</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0033</v>
+        <v>0.0502</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3971</v>
+        <v>1.5362</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0984</v>
+        <v>0.6829</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>M. NAKIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1444</v>
+        <v>0.4936</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.932</v>
+        <v>0.5422</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7876</v>
+        <v>-0.0485</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3158</v>
+        <v>0.4229</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4391</v>
+        <v>0.4261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8767</v>
+        <v>-0.0033</v>
       </c>
       <c r="J10" t="n">
-        <v>1.209</v>
+        <v>0.605</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9046</v>
+        <v>0.605</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3044</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1068</v>
+        <v>-0.1821</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4655</v>
+        <v>-0.1788</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5723</v>
+        <v>-0.0033</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7644</v>
+        <v>-0.1612</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0571</v>
+        <v>-0.0984</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3511</v>
+        <v>-1.2503</v>
       </c>
       <c r="E12" t="n">
         <v>-0.3777</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9734</v>
+        <v>-0.8726</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2047</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5381</v>
+        <v>-0.4373</v>
       </c>
       <c r="T12" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4191</v>
+        <v>-6.79</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3083</v>
+        <v>-4.7801</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1108</v>
+        <v>-2.0099</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1668</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.995</v>
+        <v>0.624</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0499</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0549</v>
+        <v>0.0459</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.5316</v>
+        <v>11.5317</v>
       </c>
       <c r="E14" t="n">
-        <v>4.547499999999999</v>
+        <v>4.547399999999999</v>
       </c>
       <c r="F14" t="n">
         <v>6.984</v>
       </c>
       <c r="G14" t="n">
-        <v>7.973199999999999</v>
+        <v>7.9732</v>
       </c>
       <c r="H14" t="n">
         <v>0.3774000000000002</v>
@@ -1537,7 +1537,7 @@
         <v>3.363900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.7574</v>
@@ -1546,13 +1546,13 @@
         <v>12.7576</v>
       </c>
       <c r="S14" t="n">
-        <v>4.599600000000001</v>
+        <v>4.5994</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6343</v>
+        <v>1.6341</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9653</v>
+        <v>2.9654</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0411</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2187</v>
+        <v>2.428</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9125</v>
+        <v>2.5023</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3061</v>
+        <v>-0.0743</v>
       </c>
       <c r="G15" t="n">
         <v>2.7176</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.3618</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0376</v>
+        <v>-0.4479</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4665</v>
+        <v>0.0861</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1791</v>
+        <v>0.4251</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1763</v>
+        <v>-0.4675</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9972</v>
+        <v>0.8925</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8951</v>
+        <v>-0.4645</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9988</v>
+        <v>0.0073</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8939</v>
+        <v>-0.4718</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6566</v>
+        <v>-0.2318</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6539</v>
+        <v>0.5546</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9973</v>
+        <v>-0.7863</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5517</v>
+        <v>-0.2327</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6551</v>
+        <v>-0.5473</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8966</v>
+        <v>0.3145</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5381</v>
+        <v>0.1937</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5351</v>
+        <v>-0.2357</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0031</v>
+        <v>0.4294</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0376</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8213</v>
+        <v>0.9528</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8589</v>
+        <v>-0.8581</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4645</v>
+        <v>2.2414</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0073</v>
+        <v>1.9135</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4718</v>
+        <v>0.3279</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2318</v>
+        <v>2.7421</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5546</v>
+        <v>1.8856</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7863</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2327</v>
+        <v>-0.5007</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5473</v>
+        <v>0.0279</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3145</v>
+        <v>-0.5286</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1937</v>
+        <v>-1.0565</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5895</v>
+        <v>-0.6838</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3958</v>
+        <v>-0.3727</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4769</v>
+        <v>0.0345</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.037</v>
+        <v>1.4686</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.44</v>
+        <v>-1.4341</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2472</v>
+        <v>-0.8951</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9338</v>
+        <v>0.9988</v>
       </c>
       <c r="I18" t="n">
-        <v>1.181</v>
+        <v>-1.8939</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7766</v>
+        <v>0.6566</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6687</v>
+        <v>1.6539</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4453</v>
+        <v>-0.9973</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5294</v>
+        <v>-1.5517</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2651</v>
+        <v>-0.6551</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>-0.8966</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4406</v>
+        <v>-0.6065</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3462</v>
+        <v>-0.1727</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4338</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.696</v>
+        <v>-0.4776</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5989</v>
+        <v>-0.2729</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.295</v>
+        <v>-0.2047</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2414</v>
+        <v>0.2472</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9135</v>
+        <v>-0.9338</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3279</v>
+        <v>1.181</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7421</v>
+        <v>0.7766</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8856</v>
+        <v>-0.6687</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8564000000000001</v>
+        <v>1.4453</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5007</v>
+        <v>-0.5294</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0279</v>
+        <v>-0.2651</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5286</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8473</v>
+        <v>-0.4413</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0376</v>
+        <v>0.1103</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8096</v>
+        <v>-0.5515</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>-0.2836</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8177</v>
+        <v>-0.7955</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8802</v>
+        <v>-1.1161</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0625</v>
+        <v>0.3206</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9905</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4714</v>
+        <v>-0.4492</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6603</v>
+        <v>-0.4022</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2836</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9115</v>
+        <v>-0.9559</v>
       </c>
       <c r="E21" t="n">
         <v>-1.7542</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8427</v>
+        <v>0.7983</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9393</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4042</v>
+        <v>0.3598</v>
       </c>
       <c r="T21" t="n">
         <v>-0.326</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7301</v>
+        <v>0.6858</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9507</v>
+        <v>-1.5246</v>
       </c>
       <c r="E22" t="n">
         <v>-1.0213</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9294</v>
+        <v>-0.5033</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6719</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7995</v>
+        <v>-0.3734</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2513</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5482</v>
+        <v>-0.1221</v>
       </c>
       <c r="V22" t="n">
         <v>3.7527</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.442</v>
+        <v>-2.0324</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.44</v>
+        <v>-0.322</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0021</v>
+        <v>-1.7104</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6063</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.5858</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6967</v>
+        <v>-0.405</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5456</v>
+        <v>-3.2368</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4411</v>
+        <v>-3.2668</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1044</v>
+        <v>0.03</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8396</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.2084</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6923</v>
+        <v>-0.1333</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2074</v>
+        <v>0.3418</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1265</v>
+        <v>-4.7047</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2766</v>
+        <v>-3.6869</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8498</v>
+        <v>-1.0179</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7721</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1224</v>
+        <v>-0.7007</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.187</v>
+        <v>-0.5972</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0646</v>
+        <v>-0.1034</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.5315</v>
+        <v>-10.7452</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.984</v>
+        <v>-6.984000000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.5477</v>
+        <v>-3.7614</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.973100000000001</v>
+        <v>-7.9731</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3773999999999995</v>
+        <v>-0.3773999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-7.595999999999999</v>
@@ -2458,13 +2458,13 @@
         <v>0.01920000000000077</v>
       </c>
       <c r="K26" t="n">
-        <v>3.383</v>
+        <v>3.382999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-3.364</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.992400000000001</v>
+        <v>-7.9924</v>
       </c>
       <c r="N26" t="n">
         <v>-3.7606</v>
@@ -2482,13 +2482,13 @@
         <v>12.7575</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.599499999999999</v>
+        <v>-3.813299999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.9652</v>
+        <v>-2.9654</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.6341</v>
+        <v>-0.8476000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>1.0411</v>
@@ -2497,7 +2497,7 @@
         <v>8.7194</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.6783</v>
+        <v>-7.678300000000002</v>
       </c>
     </row>
   </sheetData>
